--- a/output/pdf_financials_xlsx/ICE.xlsx
+++ b/output/pdf_financials_xlsx/ICE.xlsx
@@ -7392,13 +7392,13 @@
         </is>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0</v>
+        <v>2.365</v>
       </c>
       <c r="M91" s="3" t="n">
-        <v>0</v>
+        <v>3.775</v>
       </c>
       <c r="N91" s="3" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O91" s="1" t="inlineStr">
         <is>
@@ -7406,19 +7406,19 @@
         </is>
       </c>
       <c r="P91" s="3" t="n">
-        <v>0</v>
+        <v>1.757</v>
       </c>
       <c r="Q91" s="3" t="n">
-        <v>0</v>
+        <v>3.662</v>
       </c>
       <c r="R91" s="3" t="n">
-        <v>0</v>
+        <v>2.832</v>
       </c>
       <c r="S91" s="3" t="n">
-        <v>0</v>
+        <v>5.794</v>
       </c>
       <c r="T91" s="3" t="n">
-        <v>0</v>
+        <v>4.054</v>
       </c>
     </row>
     <row r="92">
@@ -13337,7 +13337,11 @@
           <t>Foreign currency translation reserve</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>-</t>
@@ -21398,7 +21402,11 @@
           <t>Foreign currency translation reserve 2,365</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>GainsLossesNotAffectingRetainedEarnings</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ICE.xlsx
+++ b/output/pdf_financials_xlsx/ICE.xlsx
@@ -2916,7 +2916,7 @@
         </is>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>12.53</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>18.532</v>
@@ -3072,7 +3072,7 @@
         </is>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>12.53</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>18.532</v>
@@ -4008,7 +4008,7 @@
         </is>
       </c>
       <c r="P48" s="3" t="n">
-        <v>13.318</v>
+        <v>0.788</v>
       </c>
       <c r="Q48" s="3" t="n">
         <v>1.473</v>
@@ -9766,10 +9766,10 @@
         <v>0</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-1.027</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-1.08</v>
       </c>
       <c r="M124" s="3" t="n">
         <v>0</v>
@@ -9838,10 +9838,10 @@
         <v>0</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-1.027</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-1.08</v>
       </c>
       <c r="M125" s="3" t="n">
         <v>0</v>
@@ -15711,7 +15711,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -40937,7 +40937,11 @@
           <t>Equipment lease payments</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E282" t="inlineStr">
         <is>
           <t>-</t>
@@ -48917,7 +48921,11 @@
           <t>General and administration expenses (notes 9, 10 and 18)</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
           <t>-</t>
@@ -51403,7 +51411,11 @@
           <t>General and administration expenses (notes 12, 13 and 21)</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr"/>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E380" t="inlineStr">
         <is>
           <t>-</t>
@@ -52582,7 +52594,11 @@
           <t>General and administration expenses (notes 13, 14 and 22)</t>
         </is>
       </c>
-      <c r="D391" t="inlineStr"/>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E391" t="inlineStr">
         <is>
           <t>-</t>
@@ -53904,7 +53920,11 @@
           <t>General and administration expenses (notes 14 and 22)</t>
         </is>
       </c>
-      <c r="D403" t="inlineStr"/>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E403" t="inlineStr">
         <is>
           <t>-</t>
@@ -55316,7 +55336,11 @@
           <t>General and administration expenses (notes 13 and 21)</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr"/>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E417" t="inlineStr">
         <is>
           <t>-</t>
@@ -56800,7 +56824,11 @@
           <t>General and administration expenses (notes 13 and 21)</t>
         </is>
       </c>
-      <c r="D431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E431" t="inlineStr">
         <is>
           <t>-</t>
@@ -59087,7 +59115,11 @@
           <t>General and administration expenses (note 13 and 21)</t>
         </is>
       </c>
-      <c r="D452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E452" t="inlineStr">
         <is>
           <t>-</t>
@@ -60074,7 +60106,11 @@
           <t>General and administration expenses</t>
         </is>
       </c>
-      <c r="D461" t="inlineStr"/>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E461" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ICE.xlsx
+++ b/output/pdf_financials_xlsx/ICE.xlsx
@@ -644,15 +644,11 @@
       <c r="Q4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="R4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R4" s="3" t="n">
+        <v>73.72799999999999</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>86.151</v>
       </c>
       <c r="T4" s="1" t="inlineStr">
         <is>
@@ -806,15 +802,11 @@
       <c r="Q6" s="3" t="n">
         <v>-3.611</v>
       </c>
-      <c r="R6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R6" s="3" t="n">
+        <v>68.521</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>80.655</v>
       </c>
       <c r="T6" s="1" t="inlineStr">
         <is>
@@ -1184,15 +1176,11 @@
       <c r="Q11" s="3" t="n">
         <v>-7.343</v>
       </c>
-      <c r="R11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R11" s="3" t="n">
+        <v>61.028</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>73.14</v>
       </c>
       <c r="T11" s="1" t="inlineStr">
         <is>
@@ -1479,7 +1467,7 @@
         <v>0.011</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>0.005</v>
+        <v>0.011</v>
       </c>
       <c r="S15" s="3" t="n">
         <v>0.034</v>
@@ -2656,15 +2644,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R30" s="3" t="n">
+        <v>8.401150173611111</v>
+      </c>
+      <c r="S30" s="3" t="n">
+        <v>11.55761395688965</v>
       </c>
       <c r="T30" s="1" t="inlineStr">
         <is>
@@ -2830,15 +2814,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R32" s="3" t="n">
+        <v>0.5900065104166667</v>
+      </c>
+      <c r="S32" s="3" t="n">
+        <v>3.250107369618461</v>
       </c>
       <c r="T32" s="1" t="inlineStr">
         <is>
@@ -10691,7 +10671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W477"/>
+  <dimension ref="A1:W493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -50902,17 +50882,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B375" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
+      <c r="B375" t="inlineStr"/>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Ice rink and recreational facilities (note 19) $</t>
-        </is>
-      </c>
-      <c r="D375" t="inlineStr"/>
+          <t>Revenue $ 26,043 $ 24,617 $ 94,035 $</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
       <c r="E375" t="inlineStr">
         <is>
           <t>-</t>
@@ -50928,17 +50908,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H375" s="5" t="n">
-        <v>69.90900000000001</v>
-      </c>
-      <c r="I375" s="5" t="n">
-        <v>71.96599999999999</v>
-      </c>
-      <c r="J375" s="5" t="n">
-        <v>72.82299999999999</v>
-      </c>
-      <c r="K375" s="5" t="n">
-        <v>72.791</v>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L375" t="inlineStr">
         <is>
@@ -50950,11 +50938,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N375" s="5" t="n">
-        <v>83.07899999999999</v>
-      </c>
-      <c r="O375" s="5" t="n">
-        <v>85.411</v>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P375" t="inlineStr">
         <is>
@@ -50976,16 +50968,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="T375" s="5" t="n">
+      <c r="T375" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U375" s="5" t="n">
         <v>73.72799999999999</v>
       </c>
-      <c r="U375" s="5" t="n">
+      <c r="V375" s="5" t="n">
         <v>86.151</v>
-      </c>
-      <c r="V375" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="W375" t="inlineStr">
         <is>
@@ -50999,14 +50991,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B376" t="inlineStr">
-        <is>
-          <t>Ice rink and recreational facilities</t>
-        </is>
-      </c>
+      <c r="B376" t="inlineStr"/>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Salaries, wages and benefits (note 12)</t>
+          <t>Expenses (1) (17,612) (17,918) (69,391)</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
@@ -51085,16 +51073,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="T376" s="5" t="n">
-        <v>29.044</v>
+      <c r="T376" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="U376" s="5" t="n">
-        <v>31.654</v>
-      </c>
-      <c r="V376" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-55.729</v>
+      </c>
+      <c r="V376" s="5" t="n">
+        <v>-66.771</v>
       </c>
       <c r="W376" t="inlineStr">
         <is>
@@ -51110,12 +51098,12 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Ice rink and recreational facilities</t>
+          <t>Earnings from ice rink &amp; recreational</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Selling and customer service</t>
+          <t>Earnings from ice rink &amp; recreational facilities before the undernote 8,431 6,699 24,644</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
@@ -51164,36 +51152,46 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N377" s="5" t="n">
-        <v>11.515</v>
-      </c>
-      <c r="O377" s="5" t="n">
-        <v>11.32</v>
-      </c>
-      <c r="P377" s="5" t="n">
-        <v>11.303</v>
-      </c>
-      <c r="Q377" s="5" t="n">
-        <v>12.692</v>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P377" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q377" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R377" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S377" s="5" t="n">
-        <v>5.288</v>
-      </c>
-      <c r="T377" s="5" t="n">
-        <v>8.772</v>
+      <c r="S377" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T377" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="U377" s="5" t="n">
-        <v>10.416</v>
-      </c>
-      <c r="V377" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>17.999</v>
+      </c>
+      <c r="V377" s="5" t="n">
+        <v>19.38</v>
       </c>
       <c r="W377" t="inlineStr">
         <is>
@@ -51209,12 +51207,12 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Ice rink and recreational facilities</t>
+          <t>Earnings from ice rink &amp; recreational</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Repairs and maintenance</t>
+          <t>General &amp; administration expenses (3,249) (3,680) (10,954)</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
@@ -51233,11 +51231,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H378" s="5" t="n">
-        <v>3.095</v>
-      </c>
-      <c r="I378" s="5" t="n">
-        <v>3.555</v>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J378" t="inlineStr">
         <is>
@@ -51259,36 +51261,46 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N378" s="5" t="n">
-        <v>4.564</v>
-      </c>
-      <c r="O378" s="5" t="n">
-        <v>4.576</v>
-      </c>
-      <c r="P378" s="5" t="n">
-        <v>5.73</v>
-      </c>
-      <c r="Q378" s="5" t="n">
-        <v>7.589</v>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R378" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S378" s="5" t="n">
-        <v>2.596</v>
-      </c>
-      <c r="T378" s="5" t="n">
-        <v>6.127</v>
+      <c r="S378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="U378" s="5" t="n">
-        <v>10.168</v>
-      </c>
-      <c r="V378" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-7.355</v>
+      </c>
+      <c r="V378" s="5" t="n">
+        <v>-9.962999999999999</v>
       </c>
       <c r="W378" t="inlineStr">
         <is>
@@ -51304,12 +51316,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Ice rink and recreational facilities</t>
+          <t>Earnings from ice rink &amp; recreational</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Earnings from ice rink and recreational facilities before the undernoted</t>
+          <t>Earnings before the undernoted 5,182 3,019 13,690</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
@@ -51358,36 +51370,46 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N379" s="5" t="n">
-        <v>17.362</v>
-      </c>
-      <c r="O379" s="5" t="n">
-        <v>18.71</v>
-      </c>
-      <c r="P379" s="5" t="n">
-        <v>20.437</v>
-      </c>
-      <c r="Q379" s="5" t="n">
-        <v>19.094</v>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P379" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q379" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R379" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S379" s="5" t="n">
-        <v>11.577</v>
-      </c>
-      <c r="T379" s="5" t="n">
-        <v>17.999</v>
+      <c r="S379" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T379" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="U379" s="5" t="n">
-        <v>19.38</v>
-      </c>
-      <c r="V379" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>10.644</v>
+      </c>
+      <c r="V379" s="5" t="n">
+        <v>9.417</v>
       </c>
       <c r="W379" t="inlineStr">
         <is>
@@ -51403,19 +51425,15 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Ice rink and recreational facilities</t>
+          <t>Other gains (expenses)</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>General and administration expenses (notes 12, 13 and 21)</t>
-        </is>
-      </c>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Depreciation (1,964) (1,763) (7,558)</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr"/>
       <c r="E380" t="inlineStr">
         <is>
           <t>-</t>
@@ -51491,16 +51509,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="T380" s="5" t="n">
-        <v>7.355</v>
+      <c r="T380" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="U380" s="5" t="n">
-        <v>9.962999999999999</v>
-      </c>
-      <c r="V380" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-8.379</v>
+      </c>
+      <c r="V380" s="5" t="n">
+        <v>-7.513</v>
       </c>
       <c r="W380" t="inlineStr">
         <is>
@@ -51516,12 +51534,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Ice rink and recreational facilities</t>
+          <t>Other gains (expenses)</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Earnings before the undernoted</t>
+          <t>Finance expenses (672) (665) (2,424)</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
@@ -51540,11 +51558,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H381" s="5" t="n">
-        <v>9.718</v>
-      </c>
-      <c r="I381" s="5" t="n">
-        <v>9.848000000000001</v>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J381" t="inlineStr">
         <is>
@@ -51566,36 +51588,46 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N381" s="5" t="n">
-        <v>12.168</v>
-      </c>
-      <c r="O381" s="5" t="n">
-        <v>12.791</v>
-      </c>
-      <c r="P381" s="5" t="n">
-        <v>14.67</v>
-      </c>
-      <c r="Q381" s="5" t="n">
-        <v>13.248</v>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P381" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q381" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R381" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S381" s="5" t="n">
-        <v>5.798</v>
-      </c>
-      <c r="T381" s="5" t="n">
-        <v>10.644</v>
+      <c r="S381" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T381" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="U381" s="5" t="n">
-        <v>9.417</v>
-      </c>
-      <c r="V381" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.428</v>
+      </c>
+      <c r="V381" s="5" t="n">
+        <v>-2.195</v>
       </c>
       <c r="W381" t="inlineStr">
         <is>
@@ -51616,7 +51648,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Foreign exchange gain</t>
+          <t>Foreign exchange gain 31 - 34</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -51699,16 +51731,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="T382" s="5" t="n">
+      <c r="T382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U382" s="5" t="n">
         <v>0.011</v>
       </c>
-      <c r="U382" s="5" t="n">
+      <c r="V382" s="5" t="n">
         <v>0.005</v>
-      </c>
-      <c r="V382" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="W382" t="inlineStr">
         <is>
@@ -51729,7 +51761,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Gain on early lease termination (note 7)</t>
+          <t>Gain (loss) on interest rate swap 61 (1,682) (712)</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -51808,18 +51840,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="T383" s="5" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="U383" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V383" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T383" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U383" s="5" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="V383" s="5" t="n">
+        <v>-0.455</v>
       </c>
       <c r="W383" t="inlineStr">
         <is>
@@ -51835,12 +51865,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Finance income (expenses)</t>
+          <t>Other gains (expenses)</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Gain (loss) on interest rate swap (note 16(a))</t>
+          <t>Gain on early lease termination - - -</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -51919,11 +51949,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="T384" s="5" t="n">
-        <v>0.645</v>
+      <c r="T384" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="U384" s="5" t="n">
-        <v>-0.455</v>
+        <v>4.53</v>
       </c>
       <c r="V384" t="inlineStr">
         <is>
@@ -51944,19 +51976,15 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Finance income (expenses)</t>
+          <t>Other gains (expenses)</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Earnings (loss) before income taxes</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Gain on sale of assets - 5 9</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr"/>
       <c r="E385" t="inlineStr">
         <is>
           <t>-</t>
@@ -52027,19 +52055,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S385" s="5" t="n">
-        <v>-2.546</v>
-      </c>
-      <c r="T385" s="5" t="n">
-        <v>5.129</v>
+      <c r="S385" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T385" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="U385" s="5" t="n">
-        <v>-0.726</v>
-      </c>
-      <c r="V385" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.106</v>
+      </c>
+      <c r="V385" s="5" t="n">
+        <v>0.015</v>
       </c>
       <c r="W385" t="inlineStr">
         <is>
@@ -52055,12 +52085,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss)</t>
+          <t>Other gains (expenses)</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Total comprehensive income (loss) $</t>
+          <t>Income tax recovery (expense) (278) 1,126 (239)</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -52134,19 +52164,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S386" s="5" t="n">
-        <v>-1.292</v>
-      </c>
-      <c r="T386" s="5" t="n">
-        <v>6.635</v>
+      <c r="S386" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T386" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="U386" s="5" t="n">
-        <v>-0.395</v>
-      </c>
-      <c r="V386" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.399</v>
+      </c>
+      <c r="V386" s="5" t="n">
+        <v>1.161</v>
       </c>
       <c r="W386" t="inlineStr">
         <is>
@@ -52162,12 +52194,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Weighted average common shares issued for basic and</t>
+          <t>Other gains (expenses)</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Weighted average common shares issued for basic and diluted earnings per share calculations</t>
+          <t>Net earnings for the year $ 2,360 $ 40 $ 2,800 $</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -52176,14 +52208,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F387" s="5" t="n">
-        <v>13.337448</v>
-      </c>
-      <c r="G387" s="5" t="n">
-        <v>13.337448</v>
-      </c>
-      <c r="H387" s="5" t="n">
-        <v>13.337448</v>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I387" t="inlineStr">
         <is>
@@ -52235,19 +52273,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S387" s="5" t="n">
-        <v>13.337448</v>
-      </c>
-      <c r="T387" s="5" t="n">
-        <v>13.337448</v>
+      <c r="S387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="U387" s="5" t="n">
-        <v>13.337448</v>
-      </c>
-      <c r="V387" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.73</v>
+      </c>
+      <c r="V387" s="5" t="n">
+        <v>0.435</v>
       </c>
       <c r="W387" t="inlineStr">
         <is>
@@ -52263,12 +52303,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Other comprehensive income</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Ice rink and recreational facilities (note 20) $</t>
+          <t>(loss) 2,273 (754) 2,962</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -52322,35 +52362,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O388" s="5" t="n">
-        <v>85.411</v>
-      </c>
-      <c r="P388" s="5" t="n">
-        <v>87.63800000000001</v>
-      </c>
-      <c r="Q388" s="5" t="n">
-        <v>88.34099999999999</v>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R388" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S388" s="5" t="n">
-        <v>40.393</v>
-      </c>
-      <c r="T388" s="5" t="n">
-        <v>73.72799999999999</v>
-      </c>
-      <c r="U388" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V388" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U388" s="5" t="n">
+        <v>1.905</v>
+      </c>
+      <c r="V388" s="5" t="n">
+        <v>-0.83</v>
       </c>
       <c r="W388" t="inlineStr">
         <is>
@@ -52366,12 +52412,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Total comprehensive income</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Other income – government subsidy (note 3(h) and 23)</t>
+          <t>(loss) $ 4,633 $ (714) $ 5,762 $</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -52445,23 +52491,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S389" s="5" t="n">
-        <v>6.537</v>
+      <c r="S389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T389" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="U389" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V389" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="U389" s="5" t="n">
+        <v>6.635</v>
+      </c>
+      <c r="V389" s="5" t="n">
+        <v>-0.395</v>
       </c>
       <c r="W389" t="inlineStr">
         <is>
@@ -52477,12 +52521,12 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Ice rink and recreational facilities</t>
+          <t>Basic and fully diluted</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Salaries, wages and benefits (note 13)</t>
+          <t>Basic and fully diluted earnings per share $ 0.18 $ 0.00 $ 0.21 $</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
@@ -52556,21 +52600,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S390" s="5" t="n">
-        <v>19.022</v>
-      </c>
-      <c r="T390" s="5" t="n">
-        <v>29.044</v>
-      </c>
-      <c r="U390" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V390" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U390" s="5" t="n">
+        <v>3.5e-07</v>
+      </c>
+      <c r="V390" s="5" t="n">
+        <v>3e-08</v>
       </c>
       <c r="W390" t="inlineStr">
         <is>
@@ -52586,19 +52630,15 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Ice rink and recreational facilities</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>General and administration expenses (notes 13, 14 and 22)</t>
-        </is>
-      </c>
-      <c r="D391" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Ice rink and recreational facilities (note 19) $</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr"/>
       <c r="E391" t="inlineStr">
         <is>
           <t>-</t>
@@ -52614,25 +52654,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H391" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I391" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J391" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K391" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H391" s="5" t="n">
+        <v>69.90900000000001</v>
+      </c>
+      <c r="I391" s="5" t="n">
+        <v>71.96599999999999</v>
+      </c>
+      <c r="J391" s="5" t="n">
+        <v>72.82299999999999</v>
+      </c>
+      <c r="K391" s="5" t="n">
+        <v>72.791</v>
       </c>
       <c r="L391" t="inlineStr">
         <is>
@@ -52644,15 +52676,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N391" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O391" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N391" s="5" t="n">
+        <v>83.07899999999999</v>
+      </c>
+      <c r="O391" s="5" t="n">
+        <v>85.411</v>
       </c>
       <c r="P391" t="inlineStr">
         <is>
@@ -52669,16 +52697,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S391" s="5" t="n">
-        <v>5.779</v>
+      <c r="S391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T391" s="5" t="n">
-        <v>7.355</v>
-      </c>
-      <c r="U391" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>73.72799999999999</v>
+      </c>
+      <c r="U391" s="5" t="n">
+        <v>86.151</v>
       </c>
       <c r="V391" t="inlineStr">
         <is>
@@ -52699,19 +52727,15 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Ice rink and recreational facilities</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D392" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Salaries, wages and benefits (note 12)</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr"/>
       <c r="E392" t="inlineStr">
         <is>
           <t>-</t>
@@ -52782,16 +52806,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S392" s="5" t="n">
-        <v>-7.801</v>
+      <c r="S392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T392" s="5" t="n">
-        <v>-8.379</v>
-      </c>
-      <c r="U392" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>29.044</v>
+      </c>
+      <c r="U392" s="5" t="n">
+        <v>31.654</v>
       </c>
       <c r="V392" t="inlineStr">
         <is>
@@ -52812,12 +52836,12 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Ice rink and recreational facilities</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Gain on early lease termination (note 7)</t>
+          <t>Selling and customer service</t>
         </is>
       </c>
       <c r="D393" t="inlineStr"/>
@@ -52866,43 +52890,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N393" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O393" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P393" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q393" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N393" s="5" t="n">
+        <v>11.515</v>
+      </c>
+      <c r="O393" s="5" t="n">
+        <v>11.32</v>
+      </c>
+      <c r="P393" s="5" t="n">
+        <v>11.303</v>
+      </c>
+      <c r="Q393" s="5" t="n">
+        <v>12.692</v>
       </c>
       <c r="R393" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S393" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S393" s="5" t="n">
+        <v>5.288</v>
       </c>
       <c r="T393" s="5" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="U393" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>8.772</v>
+      </c>
+      <c r="U393" s="5" t="n">
+        <v>10.416</v>
       </c>
       <c r="V393" t="inlineStr">
         <is>
@@ -52923,12 +52935,12 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Ice rink and recreational facilities</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Gain on sale of assets (note 8)</t>
+          <t>Repairs and maintenance</t>
         </is>
       </c>
       <c r="D394" t="inlineStr"/>
@@ -52947,15 +52959,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H394" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I394" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H394" s="5" t="n">
+        <v>3.095</v>
+      </c>
+      <c r="I394" s="5" t="n">
+        <v>3.555</v>
       </c>
       <c r="J394" t="inlineStr">
         <is>
@@ -52977,25 +52985,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N394" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O394" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P394" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q394" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N394" s="5" t="n">
+        <v>4.564</v>
+      </c>
+      <c r="O394" s="5" t="n">
+        <v>4.576</v>
+      </c>
+      <c r="P394" s="5" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="Q394" s="5" t="n">
+        <v>7.589</v>
       </c>
       <c r="R394" t="inlineStr">
         <is>
@@ -53003,15 +53003,13 @@
         </is>
       </c>
       <c r="S394" s="5" t="n">
-        <v>1.51</v>
+        <v>2.596</v>
       </c>
       <c r="T394" s="5" t="n">
-        <v>0.106</v>
-      </c>
-      <c r="U394" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.127</v>
+      </c>
+      <c r="U394" s="5" t="n">
+        <v>10.168</v>
       </c>
       <c r="V394" t="inlineStr">
         <is>
@@ -53032,19 +53030,15 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Ice rink and recreational facilities</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Foreign exchange gain</t>
-        </is>
-      </c>
-      <c r="D395" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Earnings from ice rink and recreational facilities before the undernoted</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr"/>
       <c r="E395" t="inlineStr">
         <is>
           <t>-</t>
@@ -53090,25 +53084,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N395" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O395" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P395" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q395" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N395" s="5" t="n">
+        <v>17.362</v>
+      </c>
+      <c r="O395" s="5" t="n">
+        <v>18.71</v>
+      </c>
+      <c r="P395" s="5" t="n">
+        <v>20.437</v>
+      </c>
+      <c r="Q395" s="5" t="n">
+        <v>19.094</v>
       </c>
       <c r="R395" t="inlineStr">
         <is>
@@ -53116,15 +53102,13 @@
         </is>
       </c>
       <c r="S395" s="5" t="n">
-        <v>0.019</v>
+        <v>11.577</v>
       </c>
       <c r="T395" s="5" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="U395" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>17.999</v>
+      </c>
+      <c r="U395" s="5" t="n">
+        <v>19.38</v>
       </c>
       <c r="V395" t="inlineStr">
         <is>
@@ -53145,17 +53129,17 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Ice rink and recreational facilities</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Other income (expenses) total</t>
+          <t>General and administration expenses (notes 12, 13 and 21)</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -53228,16 +53212,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S396" s="5" t="n">
-        <v>6.272</v>
+      <c r="S396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T396" s="5" t="n">
-        <v>3.732</v>
-      </c>
-      <c r="U396" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7.355</v>
+      </c>
+      <c r="U396" s="5" t="n">
+        <v>9.962999999999999</v>
       </c>
       <c r="V396" t="inlineStr">
         <is>
@@ -53258,12 +53242,12 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Finance income (expenses)</t>
+          <t>Ice rink and recreational facilities</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Gain on interest rate swap (note 17(a))</t>
+          <t>Earnings before the undernoted</t>
         </is>
       </c>
       <c r="D397" t="inlineStr"/>
@@ -53282,15 +53266,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H397" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I397" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H397" s="5" t="n">
+        <v>9.718</v>
+      </c>
+      <c r="I397" s="5" t="n">
+        <v>9.848000000000001</v>
       </c>
       <c r="J397" t="inlineStr">
         <is>
@@ -53312,25 +53292,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N397" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O397" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P397" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q397" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N397" s="5" t="n">
+        <v>12.168</v>
+      </c>
+      <c r="O397" s="5" t="n">
+        <v>12.791</v>
+      </c>
+      <c r="P397" s="5" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="Q397" s="5" t="n">
+        <v>13.248</v>
       </c>
       <c r="R397" t="inlineStr">
         <is>
@@ -53338,15 +53310,13 @@
         </is>
       </c>
       <c r="S397" s="5" t="n">
-        <v>0.513</v>
+        <v>5.798</v>
       </c>
       <c r="T397" s="5" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="U397" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>10.644</v>
+      </c>
+      <c r="U397" s="5" t="n">
+        <v>9.417</v>
       </c>
       <c r="V397" t="inlineStr">
         <is>
@@ -53367,17 +53337,17 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Income tax expense (recovery)</t>
+          <t>Other gains (expenses)</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Net earnings (loss) for the year</t>
+          <t>Foreign exchange gain</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -53450,16 +53420,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S398" s="5" t="n">
-        <v>-1.092</v>
+      <c r="S398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T398" s="5" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="U398" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.011</v>
+      </c>
+      <c r="U398" s="5" t="n">
+        <v>0.005</v>
       </c>
       <c r="V398" t="inlineStr">
         <is>
@@ -53480,12 +53450,12 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss)</t>
+          <t>Other gains (expenses)</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Basic and fully diluted earnings (loss) per share $</t>
+          <t>Gain on early lease termination (note 7)</t>
         </is>
       </c>
       <c r="D399" t="inlineStr"/>
@@ -53559,11 +53529,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S399" s="5" t="n">
-        <v>-8e-08</v>
+      <c r="S399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T399" s="5" t="n">
-        <v>3.5e-07</v>
+        <v>4.53</v>
       </c>
       <c r="U399" t="inlineStr">
         <is>
@@ -53589,12 +53561,12 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Ice rink and recreational facilities</t>
+          <t>Finance income (expenses)</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Salaries, wages and benefits</t>
+          <t>Gain (loss) on interest rate swap (note 16(a))</t>
         </is>
       </c>
       <c r="D400" t="inlineStr"/>
@@ -53613,11 +53585,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H400" s="5" t="n">
-        <v>25.899</v>
-      </c>
-      <c r="I400" s="5" t="n">
-        <v>26.621</v>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J400" t="inlineStr">
         <is>
@@ -53639,17 +53615,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N400" s="5" t="n">
-        <v>31.608</v>
-      </c>
-      <c r="O400" s="5" t="n">
-        <v>32.874</v>
-      </c>
-      <c r="P400" s="5" t="n">
-        <v>32.769</v>
-      </c>
-      <c r="Q400" s="5" t="n">
-        <v>32.659</v>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R400" t="inlineStr">
         <is>
@@ -53661,15 +53645,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="T400" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U400" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T400" s="5" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="U400" s="5" t="n">
+        <v>-0.455</v>
       </c>
       <c r="V400" t="inlineStr">
         <is>
@@ -53690,15 +53670,19 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Ice rink and recreational facilities</t>
+          <t>Finance income (expenses)</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="D401" t="inlineStr"/>
+          <t>Earnings (loss) before income taxes</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E401" t="inlineStr">
         <is>
           <t>-</t>
@@ -53759,28 +53743,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q401" s="5" t="n">
-        <v>0.295</v>
+      <c r="Q401" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R401" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S401" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T401" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U401" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S401" s="5" t="n">
+        <v>-2.546</v>
+      </c>
+      <c r="T401" s="5" t="n">
+        <v>5.129</v>
+      </c>
+      <c r="U401" s="5" t="n">
+        <v>-0.726</v>
       </c>
       <c r="V401" t="inlineStr">
         <is>
@@ -53801,12 +53781,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Ice rink and recreational facilities</t>
+          <t>Other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Facility lease (note 3(g))</t>
+          <t>Total comprehensive income (loss) $</t>
         </is>
       </c>
       <c r="D402" t="inlineStr"/>
@@ -53865,8 +53845,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P402" s="5" t="n">
-        <v>1.38</v>
+      <c r="P402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q402" t="inlineStr">
         <is>
@@ -53878,20 +53860,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="S402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S402" s="5" t="n">
+        <v>-1.292</v>
+      </c>
+      <c r="T402" s="5" t="n">
+        <v>6.635</v>
+      </c>
+      <c r="U402" s="5" t="n">
+        <v>-0.395</v>
       </c>
       <c r="V402" t="inlineStr">
         <is>
@@ -53912,38 +53888,28 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Ice rink and recreational facilities</t>
+          <t>Weighted average common shares issued for basic and</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>General and administration expenses (notes 14 and 22)</t>
-        </is>
-      </c>
-      <c r="D403" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Weighted average common shares issued for basic and diluted earnings per share calculations</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr"/>
       <c r="E403" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F403" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G403" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H403" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F403" s="5" t="n">
+        <v>13.337448</v>
+      </c>
+      <c r="G403" s="5" t="n">
+        <v>13.337448</v>
+      </c>
+      <c r="H403" s="5" t="n">
+        <v>13.337448</v>
       </c>
       <c r="I403" t="inlineStr">
         <is>
@@ -53975,34 +53941,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O403" s="5" t="n">
-        <v>5.919</v>
-      </c>
-      <c r="P403" s="5" t="n">
-        <v>5.767</v>
-      </c>
-      <c r="Q403" s="5" t="n">
-        <v>5.846</v>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R403" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S403" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T403" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U403" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S403" s="5" t="n">
+        <v>13.337448</v>
+      </c>
+      <c r="T403" s="5" t="n">
+        <v>13.337448</v>
+      </c>
+      <c r="U403" s="5" t="n">
+        <v>13.337448</v>
       </c>
       <c r="V403" t="inlineStr">
         <is>
@@ -54023,19 +53989,15 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D404" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Ice rink and recreational facilities (note 20) $</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr"/>
       <c r="E404" t="inlineStr">
         <is>
           <t>-</t>
@@ -54051,50 +54013,60 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H404" s="5" t="n">
-        <v>4.986</v>
-      </c>
-      <c r="I404" s="5" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="J404" s="5" t="n">
-        <v>5.112</v>
-      </c>
-      <c r="K404" s="5" t="n">
-        <v>5.633</v>
-      </c>
-      <c r="L404" s="5" t="n">
-        <v>6.132</v>
-      </c>
-      <c r="M404" s="5" t="n">
-        <v>6.954</v>
-      </c>
-      <c r="N404" s="5" t="n">
-        <v>7.017</v>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O404" s="5" t="n">
-        <v>6.951</v>
+        <v>85.411</v>
       </c>
       <c r="P404" s="5" t="n">
-        <v>6.929</v>
+        <v>87.63800000000001</v>
       </c>
       <c r="Q404" s="5" t="n">
-        <v>7.946</v>
+        <v>88.34099999999999</v>
       </c>
       <c r="R404" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S404" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T404" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S404" s="5" t="n">
+        <v>40.393</v>
+      </c>
+      <c r="T404" s="5" t="n">
+        <v>73.72799999999999</v>
       </c>
       <c r="U404" t="inlineStr">
         <is>
@@ -54120,12 +54092,12 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Gain on sale of assets</t>
+          <t>Other income – government subsidy (note 3(h) and 23)</t>
         </is>
       </c>
       <c r="D405" t="inlineStr"/>
@@ -54174,27 +54146,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N405" s="5" t="n">
-        <v>-0.021</v>
-      </c>
-      <c r="O405" s="5" t="n">
-        <v>-0.007</v>
-      </c>
-      <c r="P405" s="5" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="Q405" s="5" t="n">
-        <v>-1.614</v>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q405" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R405" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S405" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S405" s="5" t="n">
+        <v>6.537</v>
       </c>
       <c r="T405" t="inlineStr">
         <is>
@@ -54225,19 +54203,15 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Ice rink and recreational facilities</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Foreign exchange loss (gain)</t>
-        </is>
-      </c>
-      <c r="D406" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Salaries, wages and benefits (note 13)</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr"/>
       <c r="E406" t="inlineStr">
         <is>
           <t>-</t>
@@ -54278,35 +54252,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M406" s="5" t="n">
-        <v>1.053</v>
-      </c>
-      <c r="N406" s="5" t="n">
-        <v>-0.474</v>
-      </c>
-      <c r="O406" s="5" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="P406" s="5" t="n">
-        <v>-0.091</v>
-      </c>
-      <c r="Q406" s="5" t="n">
-        <v>0.044</v>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q406" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R406" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S406" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T406" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S406" s="5" t="n">
+        <v>19.022</v>
+      </c>
+      <c r="T406" s="5" t="n">
+        <v>29.044</v>
       </c>
       <c r="U406" t="inlineStr">
         <is>
@@ -54332,70 +54312,94 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Ice rink and recreational facilities</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Other expenses (income) total</t>
-        </is>
-      </c>
-      <c r="D407" t="inlineStr"/>
+          <t>General and administration expenses (notes 13, 14 and 22)</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E407" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F407" s="5" t="n">
-        <v>9.087</v>
-      </c>
-      <c r="G407" s="5" t="n">
-        <v>7.582</v>
-      </c>
-      <c r="H407" s="5" t="n">
-        <v>4.908</v>
-      </c>
-      <c r="I407" s="5" t="n">
-        <v>2.868</v>
-      </c>
-      <c r="J407" s="5" t="n">
-        <v>5.089</v>
-      </c>
-      <c r="K407" s="5" t="n">
-        <v>5.728</v>
-      </c>
-      <c r="L407" s="5" t="n">
-        <v>6.751</v>
-      </c>
-      <c r="M407" s="5" t="n">
-        <v>12.093</v>
-      </c>
-      <c r="N407" s="5" t="n">
-        <v>6.522</v>
-      </c>
-      <c r="O407" s="5" t="n">
-        <v>6.968</v>
-      </c>
-      <c r="P407" s="5" t="n">
-        <v>6.828</v>
-      </c>
-      <c r="Q407" s="5" t="n">
-        <v>6.376</v>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q407" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R407" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S407" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T407" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S407" s="5" t="n">
+        <v>5.779</v>
+      </c>
+      <c r="T407" s="5" t="n">
+        <v>7.355</v>
       </c>
       <c r="U407" t="inlineStr">
         <is>
@@ -54421,17 +54425,17 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Finance income (costs)</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Finance income</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -54449,50 +54453,66 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H408" s="5" t="n">
-        <v>0.341</v>
-      </c>
-      <c r="I408" s="5" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="J408" s="5" t="n">
-        <v>0.156</v>
-      </c>
-      <c r="K408" s="5" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="L408" s="5" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="M408" s="5" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="N408" s="5" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="O408" s="5" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="P408" s="5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Q408" s="5" t="n">
-        <v>0.323</v>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q408" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R408" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S408" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T408" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S408" s="5" t="n">
+        <v>-7.801</v>
+      </c>
+      <c r="T408" s="5" t="n">
+        <v>-8.379</v>
       </c>
       <c r="U408" t="inlineStr">
         <is>
@@ -54518,12 +54538,12 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Finance income (costs)</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Finance costs</t>
+          <t>Gain on early lease termination (note 7)</t>
         </is>
       </c>
       <c r="D409" t="inlineStr"/>
@@ -54542,35 +54562,55 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H409" s="5" t="n">
-        <v>-3.356</v>
-      </c>
-      <c r="I409" s="5" t="n">
-        <v>-3.021</v>
-      </c>
-      <c r="J409" s="5" t="n">
-        <v>-2.537</v>
-      </c>
-      <c r="K409" s="5" t="n">
-        <v>-2.462</v>
-      </c>
-      <c r="L409" s="5" t="n">
-        <v>-2.643</v>
-      </c>
-      <c r="M409" s="5" t="n">
-        <v>-2.95</v>
-      </c>
-      <c r="N409" s="5" t="n">
-        <v>-2.636</v>
-      </c>
-      <c r="O409" s="5" t="n">
-        <v>-2.241</v>
-      </c>
-      <c r="P409" s="5" t="n">
-        <v>-2.289</v>
-      </c>
-      <c r="Q409" s="5" t="n">
-        <v>-2.918</v>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q409" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R409" t="inlineStr">
         <is>
@@ -54582,10 +54622,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="T409" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="T409" s="5" t="n">
+        <v>4.53</v>
       </c>
       <c r="U409" t="inlineStr">
         <is>
@@ -54611,12 +54649,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Finance income (costs)</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Gain (loss) on interest rate swap (note 17(a))</t>
+          <t>Gain on sale of assets (note 8)</t>
         </is>
       </c>
       <c r="D410" t="inlineStr"/>
@@ -54670,29 +54708,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O410" s="5" t="n">
-        <v>1.027</v>
-      </c>
-      <c r="P410" s="5" t="n">
-        <v>-0.209</v>
-      </c>
-      <c r="Q410" s="5" t="n">
-        <v>-0.485</v>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q410" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R410" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S410" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T410" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S410" s="5" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="T410" s="5" t="n">
+        <v>0.106</v>
       </c>
       <c r="U410" t="inlineStr">
         <is>
@@ -54718,15 +54758,19 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Finance income (costs)</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Finance income (costs) total</t>
-        </is>
-      </c>
-      <c r="D411" t="inlineStr"/>
+          <t>Foreign exchange gain</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E411" t="inlineStr">
         <is>
           <t>-</t>
@@ -54742,50 +54786,66 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H411" s="5" t="n">
-        <v>-3.015</v>
-      </c>
-      <c r="I411" s="5" t="n">
-        <v>-2.867</v>
-      </c>
-      <c r="J411" s="5" t="n">
-        <v>-2.381</v>
-      </c>
-      <c r="K411" s="5" t="n">
-        <v>-2.371</v>
-      </c>
-      <c r="L411" s="5" t="n">
-        <v>-2.532</v>
-      </c>
-      <c r="M411" s="5" t="n">
-        <v>-2.888</v>
-      </c>
-      <c r="N411" s="5" t="n">
-        <v>-4.629</v>
-      </c>
-      <c r="O411" s="5" t="n">
-        <v>-1.09</v>
-      </c>
-      <c r="P411" s="5" t="n">
-        <v>-2.248</v>
-      </c>
-      <c r="Q411" s="5" t="n">
-        <v>-3.08</v>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R411" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S411" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T411" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S411" s="5" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="T411" s="5" t="n">
+        <v>0.011</v>
       </c>
       <c r="U411" t="inlineStr">
         <is>
@@ -54811,17 +54871,17 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Finance income (costs)</t>
+          <t>Other income (expenses)</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Earnings before income taxes</t>
+          <t>Other income (expenses) total</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>PretaxIncome</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -54839,17 +54899,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H412" s="5" t="n">
-        <v>1.795</v>
-      </c>
-      <c r="I412" s="5" t="n">
-        <v>4.113</v>
-      </c>
-      <c r="J412" s="5" t="n">
-        <v>2.287</v>
-      </c>
-      <c r="K412" s="5" t="n">
-        <v>1.689</v>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L412" t="inlineStr">
         <is>
@@ -54861,32 +54929,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N412" s="5" t="n">
-        <v>1.017</v>
-      </c>
-      <c r="O412" s="5" t="n">
-        <v>4.733</v>
-      </c>
-      <c r="P412" s="5" t="n">
-        <v>5.594</v>
-      </c>
-      <c r="Q412" s="5" t="n">
-        <v>3.792</v>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R412" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T412" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S412" s="5" t="n">
+        <v>6.272</v>
+      </c>
+      <c r="T412" s="5" t="n">
+        <v>3.732</v>
       </c>
       <c r="U412" t="inlineStr">
         <is>
@@ -54912,19 +54984,15 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Income tax expense (recovery)</t>
+          <t>Finance income (expenses)</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Net earnings $</t>
-        </is>
-      </c>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Gain on interest rate swap (note 17(a))</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr"/>
       <c r="E413" t="inlineStr">
         <is>
           <t>-</t>
@@ -54970,32 +55038,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N413" s="5" t="n">
-        <v>1.294</v>
-      </c>
-      <c r="O413" s="5" t="n">
-        <v>3.557</v>
-      </c>
-      <c r="P413" s="5" t="n">
-        <v>4.483</v>
-      </c>
-      <c r="Q413" s="5" t="n">
-        <v>2.448</v>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R413" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S413" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T413" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S413" s="5" t="n">
+        <v>0.513</v>
+      </c>
+      <c r="T413" s="5" t="n">
+        <v>0.645</v>
       </c>
       <c r="U413" t="inlineStr">
         <is>
@@ -55021,15 +55093,19 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss)</t>
+          <t>Income tax expense (recovery)</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Total comprehensive income $</t>
-        </is>
-      </c>
-      <c r="D414" t="inlineStr"/>
+          <t>Net earnings (loss) for the year</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E414" t="inlineStr">
         <is>
           <t>-</t>
@@ -55080,29 +55156,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O414" s="5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P414" s="5" t="n">
-        <v>5.893</v>
-      </c>
-      <c r="Q414" s="5" t="n">
-        <v>0.9429999999999999</v>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R414" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S414" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T414" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S414" s="5" t="n">
+        <v>-1.092</v>
+      </c>
+      <c r="T414" s="5" t="n">
+        <v>4.73</v>
       </c>
       <c r="U414" t="inlineStr">
         <is>
@@ -55128,12 +55206,12 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Weighted average common shares issued for basic</t>
+          <t>Other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Weighted average common shares issued for basic and diluted earnings per share calculations</t>
+          <t>Basic and fully diluted earnings (loss) per share $</t>
         </is>
       </c>
       <c r="D415" t="inlineStr"/>
@@ -55152,17 +55230,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H415" s="5" t="n">
-        <v>13.337448</v>
-      </c>
-      <c r="I415" s="5" t="n">
-        <v>13.337448</v>
-      </c>
-      <c r="J415" s="5" t="n">
-        <v>13.337448</v>
-      </c>
-      <c r="K415" s="5" t="n">
-        <v>13.337448</v>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L415" t="inlineStr">
         <is>
@@ -55174,32 +55260,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N415" s="5" t="n">
-        <v>13.337448</v>
-      </c>
-      <c r="O415" s="5" t="n">
-        <v>13.337448</v>
-      </c>
-      <c r="P415" s="5" t="n">
-        <v>13.337448</v>
-      </c>
-      <c r="Q415" s="5" t="n">
-        <v>13.337448</v>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R415" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S415" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T415" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="S415" s="5" t="n">
+        <v>-8e-08</v>
+      </c>
+      <c r="T415" s="5" t="n">
+        <v>3.5e-07</v>
       </c>
       <c r="U415" t="inlineStr">
         <is>
@@ -55230,7 +55320,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Facility lease</t>
+          <t>Salaries, wages and benefits</t>
         </is>
       </c>
       <c r="D416" t="inlineStr"/>
@@ -55250,10 +55340,10 @@
         </is>
       </c>
       <c r="H416" s="5" t="n">
-        <v>1.459</v>
+        <v>25.899</v>
       </c>
       <c r="I416" s="5" t="n">
-        <v>1.657</v>
+        <v>26.621</v>
       </c>
       <c r="J416" t="inlineStr">
         <is>
@@ -55276,18 +55366,16 @@
         </is>
       </c>
       <c r="N416" s="5" t="n">
-        <v>1.184</v>
+        <v>31.608</v>
       </c>
       <c r="O416" s="5" t="n">
-        <v>1.188</v>
+        <v>32.874</v>
       </c>
       <c r="P416" s="5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Q416" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>32.769</v>
+      </c>
+      <c r="Q416" s="5" t="n">
+        <v>32.659</v>
       </c>
       <c r="R416" t="inlineStr">
         <is>
@@ -55333,14 +55421,10 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>General and administration expenses (notes 13 and 21)</t>
-        </is>
-      </c>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr"/>
       <c r="E417" t="inlineStr">
         <is>
           <t>-</t>
@@ -55386,21 +55470,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N417" s="5" t="n">
-        <v>5.194</v>
-      </c>
-      <c r="O417" s="5" t="n">
-        <v>5.919</v>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P417" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q417" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q417" s="5" t="n">
+        <v>0.295</v>
       </c>
       <c r="R417" t="inlineStr">
         <is>
@@ -55441,12 +55527,12 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Finance income (costs)</t>
+          <t>Ice rink and recreational facilities</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Fee on settlement of debt (note 10)</t>
+          <t>Facility lease (note 3(g))</t>
         </is>
       </c>
       <c r="D418" t="inlineStr"/>
@@ -55495,18 +55581,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N418" s="5" t="n">
-        <v>-2.318</v>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O418" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P418" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P418" s="5" t="n">
+        <v>1.38</v>
       </c>
       <c r="Q418" t="inlineStr">
         <is>
@@ -55552,15 +55638,19 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Finance income (costs)</t>
+          <t>Ice rink and recreational facilities</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Gain on financial assets held for trading (note 16a)</t>
-        </is>
-      </c>
-      <c r="D419" t="inlineStr"/>
+          <t>General and administration expenses (notes 14 and 22)</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E419" t="inlineStr">
         <is>
           <t>-</t>
@@ -55606,21 +55696,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N419" s="5" t="n">
-        <v>0.259</v>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O419" s="5" t="n">
-        <v>1.027</v>
-      </c>
-      <c r="P419" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q419" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.919</v>
+      </c>
+      <c r="P419" s="5" t="n">
+        <v>5.767</v>
+      </c>
+      <c r="Q419" s="5" t="n">
+        <v>5.846</v>
       </c>
       <c r="R419" t="inlineStr">
         <is>
@@ -55661,15 +55749,19 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Other comprehensive income (loss)</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Foreign currency translation differences $</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr"/>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E420" t="inlineStr">
         <is>
           <t>-</t>
@@ -55685,51 +55777,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H420" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I420" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J420" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K420" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L420" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M420" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H420" s="5" t="n">
+        <v>4.986</v>
+      </c>
+      <c r="I420" s="5" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="J420" s="5" t="n">
+        <v>5.112</v>
+      </c>
+      <c r="K420" s="5" t="n">
+        <v>5.633</v>
+      </c>
+      <c r="L420" s="5" t="n">
+        <v>6.132</v>
+      </c>
+      <c r="M420" s="5" t="n">
+        <v>6.954</v>
       </c>
       <c r="N420" s="5" t="n">
-        <v>-0.39</v>
+        <v>7.017</v>
       </c>
       <c r="O420" s="5" t="n">
-        <v>-0.857</v>
-      </c>
-      <c r="P420" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q420" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.951</v>
+      </c>
+      <c r="P420" s="5" t="n">
+        <v>6.929</v>
+      </c>
+      <c r="Q420" s="5" t="n">
+        <v>7.946</v>
       </c>
       <c r="R420" t="inlineStr">
         <is>
@@ -55770,12 +55846,12 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Ice rink and recreational facilities (note 19)</t>
+          <t>Gain on sale of assets</t>
         </is>
       </c>
       <c r="D421" t="inlineStr"/>
@@ -55814,29 +55890,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L421" s="5" t="n">
-        <v>75.732</v>
-      </c>
-      <c r="M421" s="5" t="n">
-        <v>79.449</v>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N421" s="5" t="n">
-        <v>83.07899999999999</v>
-      </c>
-      <c r="O421" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P421" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q421" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.021</v>
+      </c>
+      <c r="O421" s="5" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="P421" s="5" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="Q421" s="5" t="n">
+        <v>-1.614</v>
       </c>
       <c r="R421" t="inlineStr">
         <is>
@@ -55877,15 +55951,19 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Ice rinks and recreational facilities</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Salaries, wages and benefits</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr"/>
+          <t>Foreign exchange loss (gain)</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E422" t="inlineStr">
         <is>
           <t>-</t>
@@ -55911,35 +55989,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J422" s="5" t="n">
-        <v>27.718</v>
-      </c>
-      <c r="K422" s="5" t="n">
-        <v>28.131</v>
-      </c>
-      <c r="L422" s="5" t="n">
-        <v>28.87</v>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M422" s="5" t="n">
-        <v>30.451</v>
+        <v>1.053</v>
       </c>
       <c r="N422" s="5" t="n">
-        <v>31.608</v>
-      </c>
-      <c r="O422" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P422" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q422" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.474</v>
+      </c>
+      <c r="O422" s="5" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="P422" s="5" t="n">
+        <v>-0.091</v>
+      </c>
+      <c r="Q422" s="5" t="n">
+        <v>0.044</v>
       </c>
       <c r="R422" t="inlineStr">
         <is>
@@ -55980,12 +56058,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Ice rinks and recreational facilities</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Selling and customer service</t>
+          <t>Other expenses (income) total</t>
         </is>
       </c>
       <c r="D423" t="inlineStr"/>
@@ -55994,59 +56072,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F423" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G423" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H423" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I423" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J423" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K423" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F423" s="5" t="n">
+        <v>9.087</v>
+      </c>
+      <c r="G423" s="5" t="n">
+        <v>7.582</v>
+      </c>
+      <c r="H423" s="5" t="n">
+        <v>4.908</v>
+      </c>
+      <c r="I423" s="5" t="n">
+        <v>2.868</v>
+      </c>
+      <c r="J423" s="5" t="n">
+        <v>5.089</v>
+      </c>
+      <c r="K423" s="5" t="n">
+        <v>5.728</v>
       </c>
       <c r="L423" s="5" t="n">
-        <v>10.514</v>
+        <v>6.751</v>
       </c>
       <c r="M423" s="5" t="n">
-        <v>11.641</v>
+        <v>12.093</v>
       </c>
       <c r="N423" s="5" t="n">
-        <v>11.515</v>
-      </c>
-      <c r="O423" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P423" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q423" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>6.522</v>
+      </c>
+      <c r="O423" s="5" t="n">
+        <v>6.968</v>
+      </c>
+      <c r="P423" s="5" t="n">
+        <v>6.828</v>
+      </c>
+      <c r="Q423" s="5" t="n">
+        <v>6.376</v>
       </c>
       <c r="R423" t="inlineStr">
         <is>
@@ -56087,15 +56147,19 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Ice rinks and recreational facilities</t>
+          <t>Finance income (costs)</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-      <c r="D424" t="inlineStr"/>
+          <t>Finance income</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E424" t="inlineStr">
         <is>
           <t>-</t>
@@ -56111,45 +56175,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H424" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I424" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H424" s="5" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="I424" s="5" t="n">
+        <v>0.154</v>
       </c>
       <c r="J424" s="5" t="n">
-        <v>6.692</v>
+        <v>0.156</v>
       </c>
       <c r="K424" s="5" t="n">
-        <v>6.201</v>
+        <v>0.091</v>
       </c>
       <c r="L424" s="5" t="n">
-        <v>6.811</v>
+        <v>0.111</v>
       </c>
       <c r="M424" s="5" t="n">
-        <v>7.756</v>
+        <v>0.062</v>
       </c>
       <c r="N424" s="5" t="n">
-        <v>8.154999999999999</v>
-      </c>
-      <c r="O424" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P424" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q424" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.066</v>
+      </c>
+      <c r="O424" s="5" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="P424" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q424" s="5" t="n">
+        <v>0.323</v>
       </c>
       <c r="R424" t="inlineStr">
         <is>
@@ -56190,19 +56244,15 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Ice rinks and recreational facilities</t>
+          <t>Finance income (costs)</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Cost of goods sold</t>
-        </is>
-      </c>
-      <c r="D425" t="inlineStr">
-        <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
+          <t>Finance costs</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr"/>
       <c r="E425" t="inlineStr">
         <is>
           <t>-</t>
@@ -56218,45 +56268,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H425" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I425" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H425" s="5" t="n">
+        <v>-3.356</v>
+      </c>
+      <c r="I425" s="5" t="n">
+        <v>-3.021</v>
       </c>
       <c r="J425" s="5" t="n">
-        <v>5.486</v>
+        <v>-2.537</v>
       </c>
       <c r="K425" s="5" t="n">
-        <v>5.518</v>
+        <v>-2.462</v>
       </c>
       <c r="L425" s="5" t="n">
-        <v>5.575</v>
+        <v>-2.643</v>
       </c>
       <c r="M425" s="5" t="n">
-        <v>5.64</v>
+        <v>-2.95</v>
       </c>
       <c r="N425" s="5" t="n">
-        <v>5.668</v>
-      </c>
-      <c r="O425" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P425" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q425" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.636</v>
+      </c>
+      <c r="O425" s="5" t="n">
+        <v>-2.241</v>
+      </c>
+      <c r="P425" s="5" t="n">
+        <v>-2.289</v>
+      </c>
+      <c r="Q425" s="5" t="n">
+        <v>-2.918</v>
       </c>
       <c r="R425" t="inlineStr">
         <is>
@@ -56297,12 +56337,12 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Ice rinks and recreational facilities</t>
+          <t>Finance income (costs)</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Repairs and maintenance</t>
+          <t>Gain (loss) on interest rate swap (note 17(a))</t>
         </is>
       </c>
       <c r="D426" t="inlineStr"/>
@@ -56331,35 +56371,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J426" s="5" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="K426" s="5" t="n">
-        <v>3.641</v>
-      </c>
-      <c r="L426" s="5" t="n">
-        <v>4.128</v>
-      </c>
-      <c r="M426" s="5" t="n">
-        <v>4.135</v>
-      </c>
-      <c r="N426" s="5" t="n">
-        <v>4.564</v>
-      </c>
-      <c r="O426" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P426" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q426" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O426" s="5" t="n">
+        <v>1.027</v>
+      </c>
+      <c r="P426" s="5" t="n">
+        <v>-0.209</v>
+      </c>
+      <c r="Q426" s="5" t="n">
+        <v>-0.485</v>
       </c>
       <c r="R426" t="inlineStr">
         <is>
@@ -56400,12 +56444,12 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Ice rinks and recreational facilities</t>
+          <t>Finance income (costs)</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Property tax</t>
+          <t>Finance income (costs) total</t>
         </is>
       </c>
       <c r="D427" t="inlineStr"/>
@@ -56424,45 +56468,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H427" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I427" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H427" s="5" t="n">
+        <v>-3.015</v>
+      </c>
+      <c r="I427" s="5" t="n">
+        <v>-2.867</v>
       </c>
       <c r="J427" s="5" t="n">
-        <v>2.781</v>
+        <v>-2.381</v>
       </c>
       <c r="K427" s="5" t="n">
-        <v>2.634</v>
+        <v>-2.371</v>
       </c>
       <c r="L427" s="5" t="n">
-        <v>2.597</v>
+        <v>-2.532</v>
       </c>
       <c r="M427" s="5" t="n">
-        <v>2.987</v>
+        <v>-2.888</v>
       </c>
       <c r="N427" s="5" t="n">
-        <v>3.023</v>
-      </c>
-      <c r="O427" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P427" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q427" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4.629</v>
+      </c>
+      <c r="O427" s="5" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="P427" s="5" t="n">
+        <v>-2.248</v>
+      </c>
+      <c r="Q427" s="5" t="n">
+        <v>-3.08</v>
       </c>
       <c r="R427" t="inlineStr">
         <is>
@@ -56503,15 +56537,19 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Ice rinks and recreational facilities</t>
+          <t>Finance income (costs)</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Facility lease</t>
-        </is>
-      </c>
-      <c r="D428" t="inlineStr"/>
+          <t>Earnings before income taxes</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
           <t>-</t>
@@ -56527,45 +56565,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H428" s="5" t="n">
+        <v>1.795</v>
+      </c>
+      <c r="I428" s="5" t="n">
+        <v>4.113</v>
       </c>
       <c r="J428" s="5" t="n">
-        <v>1.781</v>
+        <v>2.287</v>
       </c>
       <c r="K428" s="5" t="n">
-        <v>1.759</v>
-      </c>
-      <c r="L428" s="5" t="n">
-        <v>1.594</v>
-      </c>
-      <c r="M428" s="5" t="n">
-        <v>1.159</v>
+        <v>1.689</v>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N428" s="5" t="n">
-        <v>1.184</v>
-      </c>
-      <c r="O428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q428" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.017</v>
+      </c>
+      <c r="O428" s="5" t="n">
+        <v>4.733</v>
+      </c>
+      <c r="P428" s="5" t="n">
+        <v>5.594</v>
+      </c>
+      <c r="Q428" s="5" t="n">
+        <v>3.792</v>
       </c>
       <c r="R428" t="inlineStr">
         <is>
@@ -56606,15 +56638,19 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Ice rinks and recreational facilities</t>
+          <t>Income tax expense (recovery)</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Ice rinks and recreational facilities total</t>
-        </is>
-      </c>
-      <c r="D429" t="inlineStr"/>
+          <t>Net earnings $</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E429" t="inlineStr">
         <is>
           <t>-</t>
@@ -56640,35 +56676,37 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J429" s="5" t="n">
-        <v>57.912</v>
-      </c>
-      <c r="K429" s="5" t="n">
-        <v>58.769</v>
-      </c>
-      <c r="L429" s="5" t="n">
-        <v>60.089</v>
-      </c>
-      <c r="M429" s="5" t="n">
-        <v>63.769</v>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N429" s="5" t="n">
-        <v>65.717</v>
-      </c>
-      <c r="O429" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P429" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q429" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.294</v>
+      </c>
+      <c r="O429" s="5" t="n">
+        <v>3.557</v>
+      </c>
+      <c r="P429" s="5" t="n">
+        <v>4.483</v>
+      </c>
+      <c r="Q429" s="5" t="n">
+        <v>2.448</v>
       </c>
       <c r="R429" t="inlineStr">
         <is>
@@ -56709,12 +56747,12 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Ice rinks and recreational facilities</t>
+          <t>Other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Earnings from ice rink and recreational facilities before the undernoted</t>
+          <t>Total comprehensive income $</t>
         </is>
       </c>
       <c r="D430" t="inlineStr"/>
@@ -56753,29 +56791,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L430" s="5" t="n">
-        <v>15.643</v>
-      </c>
-      <c r="M430" s="5" t="n">
-        <v>15.68</v>
-      </c>
-      <c r="N430" s="5" t="n">
-        <v>17.362</v>
-      </c>
-      <c r="O430" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P430" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q430" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O430" s="5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P430" s="5" t="n">
+        <v>5.893</v>
+      </c>
+      <c r="Q430" s="5" t="n">
+        <v>0.9429999999999999</v>
       </c>
       <c r="R430" t="inlineStr">
         <is>
@@ -56816,19 +56854,15 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Ice rinks and recreational facilities</t>
+          <t>Weighted average common shares issued for basic</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>General and administration expenses (notes 13 and 21)</t>
-        </is>
-      </c>
-      <c r="D431" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Weighted average common shares issued for basic and diluted earnings per share calculations</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr"/>
       <c r="E431" t="inlineStr">
         <is>
           <t>-</t>
@@ -56844,45 +56878,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H431" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I431" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H431" s="5" t="n">
+        <v>13.337448</v>
+      </c>
+      <c r="I431" s="5" t="n">
+        <v>13.337448</v>
       </c>
       <c r="J431" s="5" t="n">
-        <v>5.154</v>
+        <v>13.337448</v>
       </c>
       <c r="K431" s="5" t="n">
-        <v>4.234</v>
-      </c>
-      <c r="L431" s="5" t="n">
-        <v>4.559</v>
-      </c>
-      <c r="M431" s="5" t="n">
-        <v>4.304</v>
+        <v>13.337448</v>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N431" s="5" t="n">
-        <v>5.194</v>
-      </c>
-      <c r="O431" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P431" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q431" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>13.337448</v>
+      </c>
+      <c r="O431" s="5" t="n">
+        <v>13.337448</v>
+      </c>
+      <c r="P431" s="5" t="n">
+        <v>13.337448</v>
+      </c>
+      <c r="Q431" s="5" t="n">
+        <v>13.337448</v>
       </c>
       <c r="R431" t="inlineStr">
         <is>
@@ -56923,12 +56951,12 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Ice rinks and recreational facilities</t>
+          <t>Ice rink and recreational facilities</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Earnings before the undernoted</t>
+          <t>Facility lease</t>
         </is>
       </c>
       <c r="D432" t="inlineStr"/>
@@ -56947,40 +56975,40 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H432" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I432" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J432" s="5" t="n">
-        <v>9.757</v>
-      </c>
-      <c r="K432" s="5" t="n">
-        <v>9.788</v>
-      </c>
-      <c r="L432" s="5" t="n">
-        <v>11.084</v>
-      </c>
-      <c r="M432" s="5" t="n">
-        <v>11.376</v>
+      <c r="H432" s="5" t="n">
+        <v>1.459</v>
+      </c>
+      <c r="I432" s="5" t="n">
+        <v>1.657</v>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N432" s="5" t="n">
-        <v>12.168</v>
-      </c>
-      <c r="O432" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P432" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.184</v>
+      </c>
+      <c r="O432" s="5" t="n">
+        <v>1.188</v>
+      </c>
+      <c r="P432" s="5" t="n">
+        <v>1.38</v>
       </c>
       <c r="Q432" t="inlineStr">
         <is>
@@ -57026,15 +57054,19 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Ice rink and recreational facilities</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Loss (gain) on sale of assets</t>
-        </is>
-      </c>
-      <c r="D433" t="inlineStr"/>
+          <t>General and administration expenses (notes 13 and 21)</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E433" t="inlineStr">
         <is>
           <t>-</t>
@@ -57070,19 +57102,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L433" s="5" t="n">
-        <v>-0.047</v>
-      </c>
-      <c r="M433" s="5" t="n">
-        <v>0.016</v>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N433" s="5" t="n">
-        <v>-0.021</v>
-      </c>
-      <c r="O433" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.194</v>
+      </c>
+      <c r="O433" s="5" t="n">
+        <v>5.919</v>
       </c>
       <c r="P433" t="inlineStr">
         <is>
@@ -57133,12 +57167,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Finance income (costs)</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Impairment loss (note 6)</t>
+          <t>Fee on settlement of debt (note 10)</t>
         </is>
       </c>
       <c r="D434" t="inlineStr"/>
@@ -57182,13 +57216,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M434" s="5" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="N434" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N434" s="5" t="n">
+        <v>-2.318</v>
       </c>
       <c r="O434" t="inlineStr">
         <is>
@@ -57249,7 +57283,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Gain on financial assets held for trading (note 16)</t>
+          <t>Gain on financial assets held for trading (note 16a)</t>
         </is>
       </c>
       <c r="D435" t="inlineStr"/>
@@ -57301,10 +57335,8 @@
       <c r="N435" s="5" t="n">
         <v>0.259</v>
       </c>
-      <c r="O435" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O435" s="5" t="n">
+        <v>1.027</v>
       </c>
       <c r="P435" t="inlineStr">
         <is>
@@ -57355,19 +57387,15 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Finance income (costs)</t>
+          <t>Other comprehensive income (loss)</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Earnings (loss) before income taxes</t>
-        </is>
-      </c>
-      <c r="D436" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Foreign currency translation differences $</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr"/>
       <c r="E436" t="inlineStr">
         <is>
           <t>-</t>
@@ -57403,19 +57431,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L436" s="5" t="n">
-        <v>1.801</v>
-      </c>
-      <c r="M436" s="5" t="n">
-        <v>-3.605</v>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N436" s="5" t="n">
-        <v>1.017</v>
-      </c>
-      <c r="O436" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.39</v>
+      </c>
+      <c r="O436" s="5" t="n">
+        <v>-0.857</v>
       </c>
       <c r="P436" t="inlineStr">
         <is>
@@ -57466,12 +57496,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Foreign currency translation differences                                          $(390)            $3,612</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Total comprehensive income</t>
+          <t>Ice rink and recreational facilities (note 19)</t>
         </is>
       </c>
       <c r="D437" t="inlineStr"/>
@@ -57510,16 +57540,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L437" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L437" s="5" t="n">
+        <v>75.732</v>
       </c>
       <c r="M437" s="5" t="n">
-        <v>0.01</v>
+        <v>79.449</v>
       </c>
       <c r="N437" s="5" t="n">
-        <v>0.904</v>
+        <v>83.07899999999999</v>
       </c>
       <c r="O437" t="inlineStr">
         <is>
@@ -57575,12 +57603,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Weighted average common shares issued for basic</t>
+          <t>Ice rinks and recreational facilities</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Weighted average common shares issued for basic total</t>
+          <t>Salaries, wages and benefits</t>
         </is>
       </c>
       <c r="D438" t="inlineStr"/>
@@ -57609,24 +57637,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J438" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K438" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J438" s="5" t="n">
+        <v>27.718</v>
+      </c>
+      <c r="K438" s="5" t="n">
+        <v>28.131</v>
       </c>
       <c r="L438" s="5" t="n">
-        <v>13337.448</v>
+        <v>28.87</v>
       </c>
       <c r="M438" s="5" t="n">
-        <v>13337.448</v>
+        <v>30.451</v>
       </c>
       <c r="N438" s="5" t="n">
-        <v>13337.448</v>
+        <v>31.608</v>
       </c>
       <c r="O438" t="inlineStr">
         <is>
@@ -57682,19 +57706,15 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Ice rinks and recreational facilities</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
-        </is>
-      </c>
-      <c r="D439" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Selling and customer service</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr"/>
       <c r="E439" t="inlineStr">
         <is>
           <t>-</t>
@@ -57731,15 +57751,13 @@
         </is>
       </c>
       <c r="L439" s="5" t="n">
-        <v>0.666</v>
+        <v>10.514</v>
       </c>
       <c r="M439" s="5" t="n">
-        <v>1.053</v>
-      </c>
-      <c r="N439" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>11.641</v>
+      </c>
+      <c r="N439" s="5" t="n">
+        <v>11.515</v>
       </c>
       <c r="O439" t="inlineStr">
         <is>
@@ -57795,12 +57813,12 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>Ice rinks and recreational facilities</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Foreign currency translation differences</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="D440" t="inlineStr"/>
@@ -57829,28 +57847,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J440" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K440" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L440" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J440" s="5" t="n">
+        <v>6.692</v>
+      </c>
+      <c r="K440" s="5" t="n">
+        <v>6.201</v>
+      </c>
+      <c r="L440" s="5" t="n">
+        <v>6.811</v>
       </c>
       <c r="M440" s="5" t="n">
-        <v>3.612</v>
-      </c>
-      <c r="N440" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>7.756</v>
+      </c>
+      <c r="N440" s="5" t="n">
+        <v>8.154999999999999</v>
       </c>
       <c r="O440" t="inlineStr">
         <is>
@@ -57906,15 +57916,19 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Other comprehensive income</t>
+          <t>Ice rinks and recreational facilities</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Total comprehensive income</t>
-        </is>
-      </c>
-      <c r="D441" t="inlineStr"/>
+          <t>Cost of goods sold</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
       <c r="E441" t="inlineStr">
         <is>
           <t>-</t>
@@ -57940,26 +57954,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J441" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K441" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J441" s="5" t="n">
+        <v>5.486</v>
+      </c>
+      <c r="K441" s="5" t="n">
+        <v>5.518</v>
       </c>
       <c r="L441" s="5" t="n">
-        <v>0.896</v>
+        <v>5.575</v>
       </c>
       <c r="M441" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N441" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.64</v>
+      </c>
+      <c r="N441" s="5" t="n">
+        <v>5.668</v>
       </c>
       <c r="O441" t="inlineStr">
         <is>
@@ -58020,7 +58028,7 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Selling, customer service and other</t>
+          <t>Repairs and maintenance</t>
         </is>
       </c>
       <c r="D442" t="inlineStr"/>
@@ -58050,25 +58058,19 @@
         </is>
       </c>
       <c r="J442" s="5" t="n">
-        <v>10.084</v>
+        <v>3.37</v>
       </c>
       <c r="K442" s="5" t="n">
-        <v>10.885</v>
-      </c>
-      <c r="L442" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M442" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N442" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.641</v>
+      </c>
+      <c r="L442" s="5" t="n">
+        <v>4.128</v>
+      </c>
+      <c r="M442" s="5" t="n">
+        <v>4.135</v>
+      </c>
+      <c r="N442" s="5" t="n">
+        <v>4.564</v>
       </c>
       <c r="O442" t="inlineStr">
         <is>
@@ -58129,7 +58131,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Earnings from ice rink and recreational facilities</t>
+          <t>Property tax</t>
         </is>
       </c>
       <c r="D443" t="inlineStr"/>
@@ -58159,25 +58161,19 @@
         </is>
       </c>
       <c r="J443" s="5" t="n">
-        <v>14.911</v>
+        <v>2.781</v>
       </c>
       <c r="K443" s="5" t="n">
-        <v>14.022</v>
-      </c>
-      <c r="L443" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M443" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N443" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.634</v>
+      </c>
+      <c r="L443" s="5" t="n">
+        <v>2.597</v>
+      </c>
+      <c r="M443" s="5" t="n">
+        <v>2.987</v>
+      </c>
+      <c r="N443" s="5" t="n">
+        <v>3.023</v>
       </c>
       <c r="O443" t="inlineStr">
         <is>
@@ -58233,12 +58229,12 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Ice rinks and recreational facilities</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Facility lease</t>
         </is>
       </c>
       <c r="D444" t="inlineStr"/>
@@ -58257,32 +58253,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H444" s="5" t="n">
-        <v>-0.043</v>
-      </c>
-      <c r="I444" s="5" t="n">
-        <v>0.104</v>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J444" s="5" t="n">
-        <v>-0.023</v>
+        <v>1.781</v>
       </c>
       <c r="K444" s="5" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="L444" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M444" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N444" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.759</v>
+      </c>
+      <c r="L444" s="5" t="n">
+        <v>1.594</v>
+      </c>
+      <c r="M444" s="5" t="n">
+        <v>1.159</v>
+      </c>
+      <c r="N444" s="5" t="n">
+        <v>1.184</v>
       </c>
       <c r="O444" t="inlineStr">
         <is>
@@ -58338,12 +58332,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Income tax expense</t>
+          <t>Ice rinks and recreational facilities</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Ice rinks and recreational facilities total</t>
         </is>
       </c>
       <c r="D445" t="inlineStr"/>
@@ -58372,28 +58366,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J445" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J445" s="5" t="n">
+        <v>57.912</v>
       </c>
       <c r="K445" s="5" t="n">
-        <v>0.547</v>
-      </c>
-      <c r="L445" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M445" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N445" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>58.769</v>
+      </c>
+      <c r="L445" s="5" t="n">
+        <v>60.089</v>
+      </c>
+      <c r="M445" s="5" t="n">
+        <v>63.769</v>
+      </c>
+      <c r="N445" s="5" t="n">
+        <v>65.717</v>
       </c>
       <c r="O445" t="inlineStr">
         <is>
@@ -58449,12 +58435,12 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Income tax expense</t>
+          <t>Ice rinks and recreational facilities</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Deferred</t>
+          <t>Earnings from ice rink and recreational facilities before the undernoted</t>
         </is>
       </c>
       <c r="D446" t="inlineStr"/>
@@ -58483,26 +58469,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J446" s="5" t="n">
-        <v>0.992</v>
-      </c>
-      <c r="K446" s="5" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="L446" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M446" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N446" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L446" s="5" t="n">
+        <v>15.643</v>
+      </c>
+      <c r="M446" s="5" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="N446" s="5" t="n">
+        <v>17.362</v>
       </c>
       <c r="O446" t="inlineStr">
         <is>
@@ -58558,15 +58542,19 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Income tax expense</t>
+          <t>Ice rinks and recreational facilities</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Income tax expense total</t>
-        </is>
-      </c>
-      <c r="D447" t="inlineStr"/>
+          <t>General and administration expenses (notes 13 and 21)</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E447" t="inlineStr">
         <is>
           <t>-</t>
@@ -58593,25 +58581,19 @@
         </is>
       </c>
       <c r="J447" s="5" t="n">
-        <v>0.992</v>
+        <v>5.154</v>
       </c>
       <c r="K447" s="5" t="n">
-        <v>0.593</v>
-      </c>
-      <c r="L447" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M447" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N447" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.234</v>
+      </c>
+      <c r="L447" s="5" t="n">
+        <v>4.559</v>
+      </c>
+      <c r="M447" s="5" t="n">
+        <v>4.304</v>
+      </c>
+      <c r="N447" s="5" t="n">
+        <v>5.194</v>
       </c>
       <c r="O447" t="inlineStr">
         <is>
@@ -58667,12 +58649,12 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Income tax expense</t>
+          <t>Ice rinks and recreational facilities</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Net earnings and comprehensive income $</t>
+          <t>Earnings before the undernoted</t>
         </is>
       </c>
       <c r="D448" t="inlineStr"/>
@@ -58702,25 +58684,19 @@
         </is>
       </c>
       <c r="J448" s="5" t="n">
-        <v>1.295</v>
+        <v>9.757</v>
       </c>
       <c r="K448" s="5" t="n">
-        <v>1.096</v>
-      </c>
-      <c r="L448" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M448" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N448" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>9.788</v>
+      </c>
+      <c r="L448" s="5" t="n">
+        <v>11.084</v>
+      </c>
+      <c r="M448" s="5" t="n">
+        <v>11.376</v>
+      </c>
+      <c r="N448" s="5" t="n">
+        <v>12.168</v>
       </c>
       <c r="O448" t="inlineStr">
         <is>
@@ -58776,19 +58752,15 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Income tax expense</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Basic and fully diluted earnings per share $</t>
-        </is>
-      </c>
-      <c r="D449" t="inlineStr">
-        <is>
-          <t>DilutedEPS</t>
-        </is>
-      </c>
+          <t>Loss (gain) on sale of assets</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr"/>
       <c r="E449" t="inlineStr">
         <is>
           <t>-</t>
@@ -58814,26 +58786,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J449" s="5" t="n">
-        <v>1e-07</v>
-      </c>
-      <c r="K449" s="5" t="n">
-        <v>8e-08</v>
-      </c>
-      <c r="L449" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M449" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N449" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L449" s="5" t="n">
+        <v>-0.047</v>
+      </c>
+      <c r="M449" s="5" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="N449" s="5" t="n">
+        <v>-0.021</v>
       </c>
       <c r="O449" t="inlineStr">
         <is>
@@ -58889,12 +58859,12 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Ice rink and recreational facilities</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Selling, customer service and other</t>
+          <t>Impairment loss (note 6)</t>
         </is>
       </c>
       <c r="D450" t="inlineStr"/>
@@ -58913,11 +58883,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H450" s="5" t="n">
-        <v>10.548</v>
-      </c>
-      <c r="I450" s="5" t="n">
-        <v>10.704</v>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J450" t="inlineStr">
         <is>
@@ -58934,10 +58908,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M450" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M450" s="5" t="n">
+        <v>4.07</v>
       </c>
       <c r="N450" t="inlineStr">
         <is>
@@ -58998,12 +58970,12 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Ice rink and recreational facilities</t>
+          <t>Finance income (costs)</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Earnings from ice rink and recreational facilities</t>
+          <t>Gain on financial assets held for trading (note 16)</t>
         </is>
       </c>
       <c r="D451" t="inlineStr"/>
@@ -59022,11 +58994,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H451" s="5" t="n">
-        <v>14.282</v>
-      </c>
-      <c r="I451" s="5" t="n">
-        <v>14.119</v>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J451" t="inlineStr">
         <is>
@@ -59048,10 +59024,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N451" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N451" s="5" t="n">
+        <v>0.259</v>
       </c>
       <c r="O451" t="inlineStr">
         <is>
@@ -59107,17 +59081,17 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Ice rink and recreational facilities</t>
+          <t>Finance income (costs)</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>General and administration expenses (note 13 and 21)</t>
+          <t>Earnings (loss) before income taxes</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
+          <t>PretaxIncome</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
@@ -59135,11 +59109,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H452" s="5" t="n">
-        <v>4.564</v>
-      </c>
-      <c r="I452" s="5" t="n">
-        <v>4.271</v>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J452" t="inlineStr">
         <is>
@@ -59151,20 +59129,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L452" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M452" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N452" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L452" s="5" t="n">
+        <v>1.801</v>
+      </c>
+      <c r="M452" s="5" t="n">
+        <v>-3.605</v>
+      </c>
+      <c r="N452" s="5" t="n">
+        <v>1.017</v>
       </c>
       <c r="O452" t="inlineStr">
         <is>
@@ -59220,12 +59192,12 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Foreign currency translation differences                                          $(390)            $3,612</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Gain on sale of assets (notes 6 and 7)</t>
+          <t>Total comprehensive income</t>
         </is>
       </c>
       <c r="D453" t="inlineStr"/>
@@ -59244,11 +59216,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H453" s="5" t="n">
-        <v>-0.035</v>
-      </c>
-      <c r="I453" s="5" t="n">
-        <v>-2.578</v>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J453" t="inlineStr">
         <is>
@@ -59265,15 +59241,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M453" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N453" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M453" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N453" s="5" t="n">
+        <v>0.904</v>
       </c>
       <c r="O453" t="inlineStr">
         <is>
@@ -59329,12 +59301,12 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Weighted average common shares issued for basic</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Impairment of investment property (note 7)</t>
+          <t>Weighted average common shares issued for basic total</t>
         </is>
       </c>
       <c r="D454" t="inlineStr"/>
@@ -59358,8 +59330,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I454" s="5" t="n">
-        <v>0.192</v>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J454" t="inlineStr">
         <is>
@@ -59371,20 +59345,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L454" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M454" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N454" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L454" s="5" t="n">
+        <v>13337.448</v>
+      </c>
+      <c r="M454" s="5" t="n">
+        <v>13337.448</v>
+      </c>
+      <c r="N454" s="5" t="n">
+        <v>13337.448</v>
       </c>
       <c r="O454" t="inlineStr">
         <is>
@@ -59440,17 +59408,17 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Finance income (costs)</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Deferred income tax expense (note 15)</t>
+          <t>Foreign exchange loss</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
@@ -59468,11 +59436,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H455" s="5" t="n">
-        <v>1.062</v>
-      </c>
-      <c r="I455" s="5" t="n">
-        <v>1.269</v>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J455" t="inlineStr">
         <is>
@@ -59484,15 +59456,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L455" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M455" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L455" s="5" t="n">
+        <v>0.666</v>
+      </c>
+      <c r="M455" s="5" t="n">
+        <v>1.053</v>
       </c>
       <c r="N455" t="inlineStr">
         <is>
@@ -59553,12 +59521,12 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Finance income (costs)</t>
+          <t>Other comprehensive income</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Net earnings and comprehensive income $</t>
+          <t>Foreign currency translation differences</t>
         </is>
       </c>
       <c r="D456" t="inlineStr"/>
@@ -59577,11 +59545,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H456" s="5" t="n">
-        <v>0.733</v>
-      </c>
-      <c r="I456" s="5" t="n">
-        <v>2.844</v>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J456" t="inlineStr">
         <is>
@@ -59598,10 +59570,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M456" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M456" s="5" t="n">
+        <v>3.612</v>
       </c>
       <c r="N456" t="inlineStr">
         <is>
@@ -59662,19 +59632,15 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Finance income (costs)</t>
+          <t>Other comprehensive income</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Basic and fully diluted earnings per share $</t>
-        </is>
-      </c>
-      <c r="D457" t="inlineStr">
-        <is>
-          <t>DilutedEPS</t>
-        </is>
-      </c>
+          <t>Total comprehensive income</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr"/>
       <c r="E457" t="inlineStr">
         <is>
           <t>-</t>
@@ -59690,11 +59656,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H457" s="5" t="n">
-        <v>5e-08</v>
-      </c>
-      <c r="I457" s="5" t="n">
-        <v>2.1e-07</v>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J457" t="inlineStr">
         <is>
@@ -59706,15 +59676,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L457" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M457" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L457" s="5" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="M457" s="5" t="n">
+        <v>0.01</v>
       </c>
       <c r="N457" t="inlineStr">
         <is>
@@ -59775,12 +59741,12 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Ice rinks and recreational facilities</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Ice rinks (note 15) $</t>
+          <t>Selling, customer service and other</t>
         </is>
       </c>
       <c r="D458" t="inlineStr"/>
@@ -59794,26 +59760,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G458" s="5" t="n">
-        <v>67.196</v>
-      </c>
-      <c r="H458" s="5" t="n">
-        <v>69.849</v>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I458" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J458" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K458" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J458" s="5" t="n">
+        <v>10.084</v>
+      </c>
+      <c r="K458" s="5" t="n">
+        <v>10.885</v>
       </c>
       <c r="L458" t="inlineStr">
         <is>
@@ -59884,12 +59850,12 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Ice rinks and recreational facilities</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Ice rinks</t>
+          <t>Earnings from ice rink and recreational facilities</t>
         </is>
       </c>
       <c r="D459" t="inlineStr"/>
@@ -59898,29 +59864,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F459" s="5" t="n">
-        <v>49.768</v>
-      </c>
-      <c r="G459" s="5" t="n">
-        <v>52.142</v>
-      </c>
-      <c r="H459" s="5" t="n">
-        <v>55.565</v>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I459" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J459" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K459" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J459" s="5" t="n">
+        <v>14.911</v>
+      </c>
+      <c r="K459" s="5" t="n">
+        <v>14.022</v>
       </c>
       <c r="L459" t="inlineStr">
         <is>
@@ -59991,12 +59959,12 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Ice rinks operations</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D460" t="inlineStr"/>
@@ -60005,29 +59973,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F460" s="5" t="n">
-        <v>14.901</v>
-      </c>
-      <c r="G460" s="5" t="n">
-        <v>15.054</v>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H460" s="5" t="n">
-        <v>14.284</v>
-      </c>
-      <c r="I460" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J460" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K460" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.043</v>
+      </c>
+      <c r="I460" s="5" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="J460" s="5" t="n">
+        <v>-0.023</v>
+      </c>
+      <c r="K460" s="5" t="n">
+        <v>0.095</v>
       </c>
       <c r="L460" t="inlineStr">
         <is>
@@ -60098,32 +60064,34 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income tax expense</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>General and administration expenses</t>
-        </is>
-      </c>
-      <c r="D461" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr"/>
       <c r="E461" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F461" s="5" t="n">
-        <v>3.665</v>
-      </c>
-      <c r="G461" s="5" t="n">
-        <v>4.139</v>
-      </c>
-      <c r="H461" s="5" t="n">
-        <v>4.753</v>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I461" t="inlineStr">
         <is>
@@ -60135,10 +60103,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K461" s="5" t="n">
+        <v>0.547</v>
       </c>
       <c r="L461" t="inlineStr">
         <is>
@@ -60209,12 +60175,12 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Income tax expense</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Earnings before the undernoted</t>
+          <t>Deferred</t>
         </is>
       </c>
       <c r="D462" t="inlineStr"/>
@@ -60223,29 +60189,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F462" s="5" t="n">
-        <v>11.236</v>
-      </c>
-      <c r="G462" s="5" t="n">
-        <v>10.915</v>
-      </c>
-      <c r="H462" s="5" t="n">
-        <v>9.531000000000001</v>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I462" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J462" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K462" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J462" s="5" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="K462" s="5" t="n">
+        <v>0.046</v>
       </c>
       <c r="L462" t="inlineStr">
         <is>
@@ -60316,47 +60284,45 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Income tax expense</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="D463" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>Income tax expense total</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr"/>
       <c r="E463" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F463" s="5" t="n">
-        <v>4.224</v>
-      </c>
-      <c r="G463" s="5" t="n">
-        <v>4.467</v>
-      </c>
-      <c r="H463" s="5" t="n">
-        <v>4.813</v>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I463" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J463" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K463" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J463" s="5" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="K463" s="5" t="n">
+        <v>0.593</v>
       </c>
       <c r="L463" t="inlineStr">
         <is>
@@ -60427,12 +60393,12 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Income tax expense</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Interest</t>
+          <t>Net earnings and comprehensive income $</t>
         </is>
       </c>
       <c r="D464" t="inlineStr"/>
@@ -60441,29 +60407,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F464" s="5" t="n">
-        <v>3.944</v>
-      </c>
-      <c r="G464" s="5" t="n">
-        <v>3.542</v>
-      </c>
-      <c r="H464" s="5" t="n">
-        <v>3.296</v>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I464" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J464" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K464" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J464" s="5" t="n">
+        <v>1.295</v>
+      </c>
+      <c r="K464" s="5" t="n">
+        <v>1.096</v>
       </c>
       <c r="L464" t="inlineStr">
         <is>
@@ -60534,17 +60502,17 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Income tax expense</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Foreign exchange</t>
+          <t>Basic and fully diluted earnings per share $</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>ForeignExchangeTradingGains</t>
+          <t>DilutedEPS</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
@@ -60552,29 +60520,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F465" s="5" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="G465" s="5" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="H465" s="5" t="n">
-        <v>-0.043</v>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I465" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J465" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K465" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J465" s="5" t="n">
+        <v>1e-07</v>
+      </c>
+      <c r="K465" s="5" t="n">
+        <v>8e-08</v>
       </c>
       <c r="L465" t="inlineStr">
         <is>
@@ -60645,12 +60615,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Ice rink and recreational facilities</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Sale of assets</t>
+          <t>Selling, customer service and other</t>
         </is>
       </c>
       <c r="D466" t="inlineStr"/>
@@ -60659,19 +60629,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F466" s="5" t="n">
-        <v>-0.052</v>
-      </c>
-      <c r="G466" s="5" t="n">
-        <v>-0.032</v>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H466" s="5" t="n">
-        <v>-0.035</v>
-      </c>
-      <c r="I466" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>10.548</v>
+      </c>
+      <c r="I466" s="5" t="n">
+        <v>10.704</v>
       </c>
       <c r="J466" t="inlineStr">
         <is>
@@ -60752,12 +60724,12 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Ice rink and recreational facilities</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Held-for-trading financial liabilities (note 13)</t>
+          <t>Earnings from ice rink and recreational facilities</t>
         </is>
       </c>
       <c r="D467" t="inlineStr"/>
@@ -60771,16 +60743,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G467" s="5" t="n">
-        <v>-0.365</v>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H467" s="5" t="n">
-        <v>-0.341</v>
-      </c>
-      <c r="I467" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>14.282</v>
+      </c>
+      <c r="I467" s="5" t="n">
+        <v>14.119</v>
       </c>
       <c r="J467" t="inlineStr">
         <is>
@@ -60861,17 +60833,17 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Ice rink and recreational facilities</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Earnings from operations before income taxes</t>
+          <t>General and administration expenses (note 13 and 21)</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
@@ -60879,19 +60851,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F468" s="5" t="n">
-        <v>2.149</v>
-      </c>
-      <c r="G468" s="5" t="n">
-        <v>3.333</v>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H468" s="5" t="n">
-        <v>1.841</v>
-      </c>
-      <c r="I468" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>4.564</v>
+      </c>
+      <c r="I468" s="5" t="n">
+        <v>4.271</v>
       </c>
       <c r="J468" t="inlineStr">
         <is>
@@ -60972,12 +60946,12 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Income taxes</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Future expense</t>
+          <t>Gain on sale of assets (notes 6 and 7)</t>
         </is>
       </c>
       <c r="D469" t="inlineStr"/>
@@ -60991,16 +60965,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G469" s="5" t="n">
-        <v>0.599</v>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H469" s="5" t="n">
-        <v>1.134</v>
-      </c>
-      <c r="I469" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.035</v>
+      </c>
+      <c r="I469" s="5" t="n">
+        <v>-2.578</v>
       </c>
       <c r="J469" t="inlineStr">
         <is>
@@ -61081,12 +61055,12 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>Income taxes</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Net earnings and comprehensive income</t>
+          <t>Impairment of investment property (note 7)</t>
         </is>
       </c>
       <c r="D470" t="inlineStr"/>
@@ -61095,19 +61069,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F470" s="5" t="n">
-        <v>3.827</v>
-      </c>
-      <c r="G470" s="5" t="n">
-        <v>2.734</v>
-      </c>
-      <c r="H470" s="5" t="n">
-        <v>0.707</v>
-      </c>
-      <c r="I470" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I470" s="5" t="n">
+        <v>0.192</v>
       </c>
       <c r="J470" t="inlineStr">
         <is>
@@ -61188,33 +61166,39 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>Income taxes</t>
+          <t>Finance income (costs)</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Deficit, beginning of year</t>
-        </is>
-      </c>
-      <c r="D471" t="inlineStr"/>
+          <t>Deferred income tax expense (note 15)</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E471" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F471" s="5" t="n">
-        <v>-24.04</v>
-      </c>
-      <c r="G471" s="5" t="n">
-        <v>-20.213</v>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H471" s="5" t="n">
-        <v>-17.479</v>
-      </c>
-      <c r="I471" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.062</v>
+      </c>
+      <c r="I471" s="5" t="n">
+        <v>1.269</v>
       </c>
       <c r="J471" t="inlineStr">
         <is>
@@ -61295,12 +61279,12 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Income taxes</t>
+          <t>Finance income (costs)</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Dividend on common shares (note 8)</t>
+          <t>Net earnings and comprehensive income $</t>
         </is>
       </c>
       <c r="D472" t="inlineStr"/>
@@ -61320,12 +61304,10 @@
         </is>
       </c>
       <c r="H472" s="5" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="I472" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.733</v>
+      </c>
+      <c r="I472" s="5" t="n">
+        <v>2.844</v>
       </c>
       <c r="J472" t="inlineStr">
         <is>
@@ -61406,33 +61388,39 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Income taxes</t>
+          <t>Finance income (costs)</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Deficit, end of year $</t>
-        </is>
-      </c>
-      <c r="D473" t="inlineStr"/>
+          <t>Basic and fully diluted earnings per share $</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
       <c r="E473" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F473" s="5" t="n">
-        <v>-20.213</v>
-      </c>
-      <c r="G473" s="5" t="n">
-        <v>-17.479</v>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H473" s="5" t="n">
-        <v>-16.972</v>
-      </c>
-      <c r="I473" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5e-08</v>
+      </c>
+      <c r="I473" s="5" t="n">
+        <v>2.1e-07</v>
       </c>
       <c r="J473" t="inlineStr">
         <is>
@@ -61513,12 +61501,12 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Income taxes</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Basic and fully diluted earnings per common share $</t>
+          <t>Ice rinks (note 15) $</t>
         </is>
       </c>
       <c r="D474" t="inlineStr"/>
@@ -61527,14 +61515,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F474" s="5" t="n">
-        <v>2.9e-07</v>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G474" s="5" t="n">
-        <v>2e-07</v>
+        <v>67.196</v>
       </c>
       <c r="H474" s="5" t="n">
-        <v>5e-08</v>
+        <v>69.849</v>
       </c>
       <c r="I474" t="inlineStr">
         <is>
@@ -61620,12 +61610,12 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Ice rinks (note 17) $</t>
+          <t>Ice rinks</t>
         </is>
       </c>
       <c r="D475" t="inlineStr"/>
@@ -61635,15 +61625,13 @@
         </is>
       </c>
       <c r="F475" s="5" t="n">
-        <v>64.669</v>
+        <v>49.768</v>
       </c>
       <c r="G475" s="5" t="n">
-        <v>67.196</v>
-      </c>
-      <c r="H475" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>52.142</v>
+      </c>
+      <c r="H475" s="5" t="n">
+        <v>55.565</v>
       </c>
       <c r="I475" t="inlineStr">
         <is>
@@ -61729,12 +61717,12 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Held-for-trading financial liabilities (note 15)</t>
+          <t>Ice rinks operations</t>
         </is>
       </c>
       <c r="D476" t="inlineStr"/>
@@ -61744,15 +61732,13 @@
         </is>
       </c>
       <c r="F476" s="5" t="n">
-        <v>0.9330000000000001</v>
+        <v>14.901</v>
       </c>
       <c r="G476" s="5" t="n">
-        <v>-0.365</v>
-      </c>
-      <c r="H476" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>15.054</v>
+      </c>
+      <c r="H476" s="5" t="n">
+        <v>14.284</v>
       </c>
       <c r="I476" t="inlineStr">
         <is>
@@ -61838,102 +61824,1842 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>General and administration expenses</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F477" s="5" t="n">
+        <v>3.665</v>
+      </c>
+      <c r="G477" s="5" t="n">
+        <v>4.139</v>
+      </c>
+      <c r="H477" s="5" t="n">
+        <v>4.753</v>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W477" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Earnings before the undernoted</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr"/>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F478" s="5" t="n">
+        <v>11.236</v>
+      </c>
+      <c r="G478" s="5" t="n">
+        <v>10.915</v>
+      </c>
+      <c r="H478" s="5" t="n">
+        <v>9.531000000000001</v>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W478" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Other expenses (income)</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F479" s="5" t="n">
+        <v>4.224</v>
+      </c>
+      <c r="G479" s="5" t="n">
+        <v>4.467</v>
+      </c>
+      <c r="H479" s="5" t="n">
+        <v>4.813</v>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W479" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Other expenses (income)</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Interest</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr"/>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F480" s="5" t="n">
+        <v>3.944</v>
+      </c>
+      <c r="G480" s="5" t="n">
+        <v>3.542</v>
+      </c>
+      <c r="H480" s="5" t="n">
+        <v>3.296</v>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W480" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Other expenses (income)</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Foreign exchange</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>ForeignExchangeTradingGains</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F481" s="5" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="G481" s="5" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="H481" s="5" t="n">
+        <v>-0.043</v>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W481" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Other expenses (income)</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Sale of assets</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr"/>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F482" s="5" t="n">
+        <v>-0.052</v>
+      </c>
+      <c r="G482" s="5" t="n">
+        <v>-0.032</v>
+      </c>
+      <c r="H482" s="5" t="n">
+        <v>-0.035</v>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W482" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Other expenses (income)</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Held-for-trading financial liabilities (note 13)</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr"/>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G483" s="5" t="n">
+        <v>-0.365</v>
+      </c>
+      <c r="H483" s="5" t="n">
+        <v>-0.341</v>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W483" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Other expenses (income)</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Earnings from operations before income taxes</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F484" s="5" t="n">
+        <v>2.149</v>
+      </c>
+      <c r="G484" s="5" t="n">
+        <v>3.333</v>
+      </c>
+      <c r="H484" s="5" t="n">
+        <v>1.841</v>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W484" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
           <t>Income taxes</t>
         </is>
       </c>
-      <c r="C477" t="inlineStr">
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Future expense</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr"/>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G485" s="5" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="H485" s="5" t="n">
+        <v>1.134</v>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W485" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Income taxes</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Net earnings and comprehensive income</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr"/>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F486" s="5" t="n">
+        <v>3.827</v>
+      </c>
+      <c r="G486" s="5" t="n">
+        <v>2.734</v>
+      </c>
+      <c r="H486" s="5" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W486" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Income taxes</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Deficit, beginning of year</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr"/>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F487" s="5" t="n">
+        <v>-24.04</v>
+      </c>
+      <c r="G487" s="5" t="n">
+        <v>-20.213</v>
+      </c>
+      <c r="H487" s="5" t="n">
+        <v>-17.479</v>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W487" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Income taxes</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Dividend on common shares (note 8)</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr"/>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H488" s="5" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W488" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Income taxes</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Deficit, end of year $</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr"/>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F489" s="5" t="n">
+        <v>-20.213</v>
+      </c>
+      <c r="G489" s="5" t="n">
+        <v>-17.479</v>
+      </c>
+      <c r="H489" s="5" t="n">
+        <v>-16.972</v>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W489" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Income taxes</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>Basic and fully diluted earnings per common share $</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr"/>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F490" s="5" t="n">
+        <v>2.9e-07</v>
+      </c>
+      <c r="G490" s="5" t="n">
+        <v>2e-07</v>
+      </c>
+      <c r="H490" s="5" t="n">
+        <v>5e-08</v>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W490" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Ice rinks (note 17) $</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr"/>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F491" s="5" t="n">
+        <v>64.669</v>
+      </c>
+      <c r="G491" s="5" t="n">
+        <v>67.196</v>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W491" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Other expenses (income)</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>Held-for-trading financial liabilities (note 15)</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr"/>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F492" s="5" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="G492" s="5" t="n">
+        <v>-0.365</v>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W492" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Income taxes</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
         <is>
           <t>Future (recovery) expense</t>
         </is>
       </c>
-      <c r="D477" t="inlineStr"/>
-      <c r="E477" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F477" s="5" t="n">
+      <c r="D493" t="inlineStr"/>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F493" s="5" t="n">
         <v>-1.678</v>
       </c>
-      <c r="G477" s="5" t="n">
+      <c r="G493" s="5" t="n">
         <v>0.599</v>
       </c>
-      <c r="H477" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I477" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J477" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K477" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L477" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M477" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N477" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O477" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P477" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q477" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R477" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S477" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T477" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U477" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="V477" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W477" t="inlineStr">
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V493" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W493" t="inlineStr">
         <is>
           <t>-</t>
         </is>
